--- a/data/trans_orig/IP05A05-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP05A05-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21295</t>
+          <t>20695</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35732</t>
+          <t>35493</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32310</t>
+          <t>33139</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48768</t>
+          <t>48786</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58070</t>
+          <t>56830</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80405</t>
+          <t>79718</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48055</t>
+          <t>47309</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64006</t>
+          <t>64122</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48001</t>
+          <t>48058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>64553</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>100846</t>
+          <t>101294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124309</t>
+          <t>125818</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,4%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15992</t>
+          <t>16026</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29428</t>
+          <t>30856</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17057</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31045</t>
+          <t>32150</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37013</t>
+          <t>37312</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56080</t>
+          <t>55884</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67631</t>
+          <t>69282</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91845</t>
+          <t>91879</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66236</t>
+          <t>65356</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89264</t>
+          <t>88431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>140850</t>
+          <t>141011</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>174802</t>
+          <t>174290</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,51%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>113213</t>
+          <t>111707</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>139011</t>
+          <t>139233</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>115243</t>
+          <t>114082</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>139029</t>
+          <t>140209</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>234963</t>
+          <t>235709</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>272526</t>
+          <t>270833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36717</t>
+          <t>36886</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56758</t>
+          <t>56560</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38922</t>
+          <t>39321</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60303</t>
+          <t>60143</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81482</t>
+          <t>80919</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111513</t>
+          <t>109703</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27055</t>
+          <t>26647</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43175</t>
+          <t>42886</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34268</t>
+          <t>33575</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51923</t>
+          <t>50944</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65098</t>
+          <t>63565</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>89179</t>
+          <t>87835</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57498</t>
+          <t>57238</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>75698</t>
+          <t>75449</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58378</t>
+          <t>59220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77579</t>
+          <t>78762</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>121854</t>
+          <t>121883</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>148287</t>
+          <t>148658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18753</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33579</t>
+          <t>33838</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24145</t>
+          <t>24470</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39613</t>
+          <t>40164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>46692</t>
+          <t>46525</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>67931</t>
+          <t>67669</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,21%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>49614</t>
+          <t>49673</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71224</t>
+          <t>70356</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49751</t>
+          <t>49592</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>69767</t>
+          <t>70487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105418</t>
+          <t>105024</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135220</t>
+          <t>135228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84407</t>
+          <t>84803</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107541</t>
+          <t>107354</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>97197</t>
+          <t>97133</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>119144</t>
+          <t>121036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189577</t>
+          <t>187167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>221211</t>
+          <t>218810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,46%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,78%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29479</t>
+          <t>29732</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47213</t>
+          <t>48670</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>28103</t>
+          <t>28471</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46710</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>62745</t>
+          <t>61990</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>87371</t>
+          <t>86357</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,62%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181875</t>
+          <t>184998</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>222101</t>
+          <t>223248</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>201392</t>
+          <t>199954</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238770</t>
+          <t>239758</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>396081</t>
+          <t>390977</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>452505</t>
+          <t>448218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>325203</t>
+          <t>323204</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367357</t>
+          <t>365301</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>337960</t>
+          <t>339142</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>380237</t>
+          <t>380793</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>675488</t>
+          <t>678822</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>736998</t>
+          <t>740350</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,88%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>115426</t>
+          <t>113549</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>151137</t>
+          <t>148841</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,47 +2798,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>16,71%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>21,91%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>140349</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>122456</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>157361</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>19,47%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
           <t>16,99%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>140349</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>122813</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>157003</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>247392</t>
+          <t>248684</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>295825</t>
+          <t>295430</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37026</t>
+          <t>37379</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55214</t>
+          <t>54789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39543</t>
+          <t>39730</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57633</t>
+          <t>57911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81519</t>
+          <t>80744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107012</t>
+          <t>107538</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,73%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53801</t>
+          <t>54162</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>72950</t>
+          <t>73875</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52314</t>
+          <t>52676</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72003</t>
+          <t>73323</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112598</t>
+          <t>111715</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>140695</t>
+          <t>138988</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>29253</t>
+          <t>29889</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45938</t>
+          <t>47297</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>27363</t>
+          <t>27636</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44497</t>
+          <t>44212</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>61970</t>
+          <t>61144</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>85721</t>
+          <t>86450</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69228</t>
+          <t>68197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93141</t>
+          <t>91855</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70568</t>
+          <t>71391</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>96654</t>
+          <t>97788</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>144874</t>
+          <t>146808</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180783</t>
+          <t>179575</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,54%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89767</t>
+          <t>88767</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>114381</t>
+          <t>114362</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>106893</t>
+          <t>108119</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>135547</t>
+          <t>134777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>204924</t>
+          <t>206076</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>241762</t>
+          <t>242105</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>47,92%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44437</t>
+          <t>44260</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65731</t>
+          <t>65883</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52074</t>
+          <t>52164</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76127</t>
+          <t>76903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>103053</t>
+          <t>105030</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136485</t>
+          <t>135953</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44284</t>
+          <t>44287</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63469</t>
+          <t>64554</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>41,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39847</t>
+          <t>40594</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59647</t>
+          <t>59604</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>90105</t>
+          <t>89910</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>116479</t>
+          <t>117198</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51765</t>
+          <t>52187</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71911</t>
+          <t>71676</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69895</t>
+          <t>70224</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90128</t>
+          <t>90349</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127226</t>
+          <t>126622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155613</t>
+          <t>155115</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>49,27%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32791</t>
+          <t>33024</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>51382</t>
+          <t>51191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>21558</t>
+          <t>21251</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>37173</t>
+          <t>37709</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59280</t>
+          <t>58302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>83834</t>
+          <t>82115</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48047</t>
+          <t>46950</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>67159</t>
+          <t>66581</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>39476</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57983</t>
+          <t>57689</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>91160</t>
+          <t>91156</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>118430</t>
+          <t>120554</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>63049</t>
+          <t>64660</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84201</t>
+          <t>85941</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72671</t>
+          <t>74081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>94708</t>
+          <t>97229</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>54,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>142791</t>
+          <t>143738</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174819</t>
+          <t>174752</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,85%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31424</t>
+          <t>31302</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50119</t>
+          <t>50185</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38054</t>
+          <t>37466</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56666</t>
+          <t>57430</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>73310</t>
+          <t>73051</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>101707</t>
+          <t>98924</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,22%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>216955</t>
+          <t>216147</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257434</t>
+          <t>257005</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>209951</t>
+          <t>207304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>251673</t>
+          <t>248364</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>434606</t>
+          <t>438833</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>492009</t>
+          <t>497001</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>277893</t>
+          <t>280953</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>321051</t>
+          <t>323387</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>322864</t>
+          <t>327484</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>369822</t>
+          <t>371013</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>43,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>620186</t>
+          <t>620180</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>678075</t>
+          <t>683128</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>46,68%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>153685</t>
+          <t>154053</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>190977</t>
+          <t>193515</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>156540</t>
+          <t>156655</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>195624</t>
+          <t>195820</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>322924</t>
+          <t>320982</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>376364</t>
+          <t>375092</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,63%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52133</t>
+          <t>52338</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70445</t>
+          <t>70131</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32539</t>
+          <t>32701</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>50153</t>
+          <t>49650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91315</t>
+          <t>90684</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>115349</t>
+          <t>115991</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,44%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38354</t>
+          <t>39409</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56210</t>
+          <t>56248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45218</t>
+          <t>46147</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63490</t>
+          <t>63581</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89181</t>
+          <t>88410</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113870</t>
+          <t>114130</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16140</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29902</t>
+          <t>29445</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21875</t>
+          <t>21680</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36656</t>
+          <t>36574</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>41183</t>
+          <t>40810</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>61050</t>
+          <t>62931</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67448</t>
+          <t>67415</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>90374</t>
+          <t>89395</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87571</t>
+          <t>86064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>113741</t>
+          <t>111804</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162170</t>
+          <t>162200</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194413</t>
+          <t>195801</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71952</t>
+          <t>71451</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93818</t>
+          <t>94977</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91953</t>
+          <t>91204</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117353</t>
+          <t>116789</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>170705</t>
+          <t>167668</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>203839</t>
+          <t>202557</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,23%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>39980</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59280</t>
+          <t>59398</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43063</t>
+          <t>44118</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64140</t>
+          <t>65161</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89007</t>
+          <t>89181</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116816</t>
+          <t>119655</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56008</t>
+          <t>56181</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>77441</t>
+          <t>78545</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58279</t>
+          <t>56123</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>79707</t>
+          <t>78618</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120215</t>
+          <t>119069</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>152295</t>
+          <t>150069</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>39,9%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67709</t>
+          <t>68372</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>90770</t>
+          <t>89815</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60157</t>
+          <t>60136</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>82716</t>
+          <t>83231</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134731</t>
+          <t>134204</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>164699</t>
+          <t>165217</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,79%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>34666</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>54025</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38825</t>
+          <t>39237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59142</t>
+          <t>58544</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>77923</t>
+          <t>77833</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106263</t>
+          <t>104576</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53692</t>
+          <t>52015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74470</t>
+          <t>73553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55119</t>
+          <t>55592</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>77214</t>
+          <t>77462</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114447</t>
+          <t>115618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>143629</t>
+          <t>146087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>42,2%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62230</t>
+          <t>63043</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83895</t>
+          <t>85066</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51656</t>
+          <t>52177</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>72895</t>
+          <t>72956</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>121775</t>
+          <t>121075</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>152008</t>
+          <t>150727</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,54%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27251</t>
+          <t>27181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44775</t>
+          <t>43961</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37242</t>
+          <t>36866</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>56516</t>
+          <t>56475</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67946</t>
+          <t>67812</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95611</t>
+          <t>94905</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249014</t>
+          <t>248773</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>290055</t>
+          <t>292226</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253670</t>
+          <t>252629</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>297778</t>
+          <t>296964</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>516380</t>
+          <t>515515</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>575268</t>
+          <t>575406</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>262204</t>
+          <t>261132</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>303627</t>
+          <t>302847</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>270102</t>
+          <t>270678</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>313867</t>
+          <t>314509</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>546295</t>
+          <t>543964</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>604179</t>
+          <t>603837</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,76%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133926</t>
+          <t>133665</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>168328</t>
+          <t>167702</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>158460</t>
+          <t>158795</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>196834</t>
+          <t>196631</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>301096</t>
+          <t>301763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>352918</t>
+          <t>351347</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38069</t>
+          <t>38128</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48066</t>
+          <t>48025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>40685</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51179</t>
+          <t>51038</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>82207</t>
+          <t>82229</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96442</t>
+          <t>97054</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,59%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4789</t>
+          <t>5021</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>13567</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>5737</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15509</t>
+          <t>15011</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12815</t>
+          <t>12549</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24898</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,97%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2957</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8802</t>
+          <t>8662</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6707</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>15939</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>114483</t>
+          <t>113895</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132550</t>
+          <t>132650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>127693</t>
+          <t>127884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147305</t>
+          <t>147437</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>247946</t>
+          <t>248943</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>273633</t>
+          <t>274853</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20408</t>
+          <t>21198</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>19545</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35399</t>
+          <t>35846</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>31409</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>52367</t>
+          <t>51535</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13709</t>
+          <t>13172</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29671</t>
+          <t>29408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25526</t>
+          <t>25986</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28135</t>
+          <t>28940</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49004</t>
+          <t>48421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>123144</t>
+          <t>123705</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144020</t>
+          <t>144512</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143813</t>
+          <t>144110</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>169578</t>
+          <t>170101</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>275922</t>
+          <t>273682</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>310046</t>
+          <t>308257</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>79,98%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20281</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40391</t>
+          <t>39102</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26134</t>
+          <t>26141</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49546</t>
+          <t>50268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50715</t>
+          <t>51174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81293</t>
+          <t>81562</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>5835</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17872</t>
+          <t>16444</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26737</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19519</t>
+          <t>19449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37760</t>
+          <t>39334</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>132490</t>
+          <t>140612</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>220368</t>
+          <t>219228</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>243656</t>
+          <t>243277</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>268371</t>
+          <t>268251</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>372400</t>
+          <t>368280</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>480228</t>
+          <t>480514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38167</t>
+          <t>38550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>131786</t>
+          <t>123048</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19103</t>
+          <t>19109</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37929</t>
+          <t>37458</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63000</t>
+          <t>63581</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>183661</t>
+          <t>182134</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9282</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>23799</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12852</t>
+          <t>12862</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28425</t>
+          <t>29705</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24767</t>
+          <t>26732</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48118</t>
+          <t>47320</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>431590</t>
+          <t>433761</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>525962</t>
+          <t>527522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>580265</t>
+          <t>579026</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>622231</t>
+          <t>622807</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1031056</t>
+          <t>1032372</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1135895</t>
+          <t>1132857</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,49%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>87395</t>
+          <t>86040</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>191695</t>
+          <t>194931</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>84286</t>
+          <t>82847</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>119746</t>
+          <t>119506</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>181009</t>
+          <t>181538</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>301988</t>
+          <t>282317</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>19,81%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39718</t>
+          <t>39649</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>63702</t>
+          <t>64793</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>46894</t>
+          <t>48013</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>74088</t>
+          <t>75794</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>91608</t>
+          <t>94428</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>129732</t>
+          <t>130997</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
